--- a/Development/Common/GameData/JobBase.xlsx
+++ b/Development/Common/GameData/JobBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14524ADC-E2BA-47B2-B382-447BB693A2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5082733-052B-4B97-9C31-CBCE45C9C03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38835" yWindow="6045" windowWidth="26070" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JobBase" sheetId="1" r:id="rId1"/>
@@ -108,10 +108,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Wizard</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Warrior</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -197,6 +193,10 @@
   </si>
   <si>
     <t>StatValue8</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mage</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -702,10 +702,10 @@
         <v>19</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -955,52 +955,52 @@
         <v>22</v>
       </c>
       <c r="D8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="I8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="J8" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="L8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="M8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="N8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="O8" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="P8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="Q8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="R8" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="R8" s="10" t="s">
+      <c r="S8" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="S8" s="10" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -1008,22 +1008,22 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="3">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="3">
-        <v>10</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3">
+        <v>10</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="G9" s="3">
-        <v>10</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="I9" s="3">
         <v>10</v>
@@ -1064,22 +1064,22 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="3">
-        <v>10</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3">
+        <v>10</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="G10" s="3">
-        <v>10</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="I10" s="3">
         <v>10</v>

--- a/Development/Common/GameData/JobBase.xlsx
+++ b/Development/Common/GameData/JobBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5082733-052B-4B97-9C31-CBCE45C9C03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3022A7DC-DB4B-4D23-AA3B-865C73825973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38835" yWindow="6045" windowWidth="26070" windowHeight="14340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3915" yWindow="3240" windowWidth="31605" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JobBase" sheetId="1" r:id="rId1"/>
@@ -96,10 +96,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>JobBase</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -197,6 +193,10 @@
   </si>
   <si>
     <t>Mage</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int32</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -690,7 +690,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C1" s="2"/>
     </row>
@@ -702,10 +702,10 @@
         <v>19</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>11</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>13</v>
@@ -952,55 +952,55 @@
         <v>8</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="G8" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="H8" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="I8" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I8" s="10" t="s">
-        <v>30</v>
-      </c>
       <c r="J8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="L8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="M8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="N8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="O8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="P8" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="Q8" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="Q8" s="10" t="s">
+      <c r="R8" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="R8" s="10" t="s">
+      <c r="S8" s="10" t="s">
         <v>43</v>
-      </c>
-      <c r="S8" s="10" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
@@ -1008,22 +1008,22 @@
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="3">
+        <v>10</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="3">
-        <v>10</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3">
+        <v>10</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="G9" s="3">
-        <v>10</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="I9" s="3">
         <v>10</v>
@@ -1064,22 +1064,22 @@
         <v>2</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="3">
-        <v>10</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3">
+        <v>10</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="G10" s="3">
-        <v>10</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="I10" s="3">
         <v>10</v>

--- a/Development/Common/GameData/JobBase.xlsx
+++ b/Development/Common/GameData/JobBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\MMOGameServerProject\Development\Common\GameData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3022A7DC-DB4B-4D23-AA3B-865C73825973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{994D130B-9248-495A-8B9E-73B1F7106111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3915" yWindow="3240" windowWidth="31605" windowHeight="17295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JobBase" sheetId="1" r:id="rId1"/>
@@ -1032,7 +1032,7 @@
         <v>14</v>
       </c>
       <c r="K9" s="3">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>15</v>
@@ -1088,7 +1088,7 @@
         <v>14</v>
       </c>
       <c r="K10" s="3">
-        <v>100</v>
+        <v>10000</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>15</v>
